--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,76 +706,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1751</v>
+        <v>4.544700000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1751</v>
+        <v>2.1478</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.3969</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1751</v>
+        <v>4.749499999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9225</v>
+        <v>-3.8954</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2526</v>
+        <v>8.6447</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1751</v>
+        <v>5.8444</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9225</v>
+        <v>-1.6884</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2526</v>
+        <v>7.5328</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.095</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.2069</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.1119</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.1448</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-7.7995</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.6546</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1.3724</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1641</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-1.5365</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.3125</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.9387</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6263000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -784,76 +784,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4.544700000000001</v>
+        <v>2.4525</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1478</v>
+        <v>2.5769</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3969</v>
+        <v>-0.1244000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.749499999999999</v>
+        <v>2.3397</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.8954</v>
+        <v>-1.5711</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6447</v>
+        <v>3.9107</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8444</v>
+        <v>8.3071</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6884</v>
+        <v>1.8762</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5328</v>
+        <v>6.430800000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.095</v>
+        <v>-5.9673</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2069</v>
+        <v>-3.4474</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1119</v>
+        <v>-2.5201</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1448</v>
+        <v>-4.0947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.7995</v>
+        <v>-11.1143</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6546</v>
+        <v>7.0195</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3724</v>
+        <v>1.1468</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1641</v>
+        <v>0.9938999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.5365</v>
+        <v>0.1528</v>
       </c>
       <c r="V5" t="n">
-        <v>3.3125</v>
+        <v>3.0607</v>
       </c>
       <c r="W5" t="n">
-        <v>3.9387</v>
+        <v>4.3901</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6263000000000001</v>
+        <v>-1.3293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4525</v>
+        <v>2.2389</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5769</v>
+        <v>2.1071</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1244000000000001</v>
+        <v>0.1317999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3397</v>
+        <v>-0.9382</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5711</v>
+        <v>-0.4362</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9107</v>
+        <v>-0.502</v>
       </c>
       <c r="J6" t="n">
-        <v>8.3071</v>
+        <v>0.2117</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8762</v>
+        <v>0.04969999999999997</v>
       </c>
       <c r="L6" t="n">
-        <v>6.430800000000001</v>
+        <v>0.162</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.9673</v>
+        <v>-1.1499</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.4474</v>
+        <v>-0.4859000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5201</v>
+        <v>-0.6639999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.0947</v>
+        <v>1.7549</v>
       </c>
       <c r="Q6" t="n">
-        <v>-11.1143</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>7.0195</v>
+        <v>1.7549</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1468</v>
+        <v>0.2713</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9938999999999999</v>
+        <v>0.6754</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1528</v>
+        <v>-0.4041</v>
       </c>
       <c r="V6" t="n">
-        <v>3.0607</v>
+        <v>1.151</v>
       </c>
       <c r="W6" t="n">
-        <v>4.3901</v>
+        <v>1.2201</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3293</v>
+        <v>-0.06909999999999994</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>J. CHARLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -943,73 +943,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2389</v>
+        <v>0.3125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1071</v>
+        <v>0.09809999999999963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1317999999999999</v>
+        <v>0.2146</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9382</v>
+        <v>0.7515000000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4362</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.502</v>
+        <v>-0.7284999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2117</v>
+        <v>2.4363</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04969999999999997</v>
+        <v>2.1123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.162</v>
+        <v>0.324</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1499</v>
+        <v>-1.6848</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4859000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6639999999999999</v>
+        <v>-1.0525</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7549</v>
+        <v>0.3899</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.1198</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7549</v>
+        <v>3.5097</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2713</v>
+        <v>0.6696</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6754</v>
+        <v>0.5027999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4041</v>
+        <v>0.1667999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>1.151</v>
+        <v>-1.4986</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2201</v>
+        <v>0.2786</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.06909999999999994</v>
+        <v>-1.7771</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1018,76 +1018,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.615</v>
+        <v>-1.3444</v>
       </c>
       <c r="E8" t="n">
-        <v>0.615</v>
+        <v>1.2458</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.5902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.615</v>
+        <v>-1.8337</v>
       </c>
       <c r="H8" t="n">
-        <v>0.615</v>
+        <v>2.1949</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-4.0284</v>
       </c>
       <c r="J8" t="n">
-        <v>0.615</v>
+        <v>4.1433</v>
       </c>
       <c r="K8" t="n">
-        <v>0.615</v>
+        <v>5.6353</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.4919</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-5.977</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-3.4405</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-2.5364</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3899999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-6.2395</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>6.6295</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3065</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3448</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.9617000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2073</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.9973</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-4.204499999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CHARLES</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3125</v>
+        <v>-2.7211</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09809999999999963</v>
+        <v>3.0429</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2146</v>
+        <v>-5.7641</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7515000000000002</v>
+        <v>-1.0884</v>
       </c>
       <c r="H9" t="n">
-        <v>1.48</v>
+        <v>-4.7095</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7284999999999999</v>
+        <v>3.6212</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4363</v>
+        <v>4.2701</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1123</v>
+        <v>-2.0237</v>
       </c>
       <c r="L9" t="n">
-        <v>0.324</v>
+        <v>6.2938</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6848</v>
+        <v>-5.3584</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6322</v>
+        <v>-2.6858</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0525</v>
+        <v>-2.6725</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3899</v>
+        <v>0.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1198</v>
+        <v>-6.0446</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5097</v>
+        <v>6.8245</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6696</v>
+        <v>2.3482</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5027999999999999</v>
+        <v>2.4831</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1667999999999999</v>
+        <v>-0.1349</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4986</v>
+        <v>-4.7609</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2786</v>
+        <v>2.3344</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7771</v>
+        <v>-7.0953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1174,76 +1174,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3444</v>
+        <v>-4.7439</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2458</v>
+        <v>-4.6853</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5902</v>
+        <v>-0.05859999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8337</v>
+        <v>-2.379</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1949</v>
+        <v>-0.2921</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0284</v>
+        <v>-2.0867</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1433</v>
+        <v>-1.4275</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6353</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4919</v>
+        <v>-1.9605</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.977</v>
+        <v>-0.9515</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.4405</v>
+        <v>-0.8253</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5364</v>
+        <v>-0.1262</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3899999999999999</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.2395</v>
+        <v>-2.9248</v>
       </c>
       <c r="R10" t="n">
-        <v>6.6295</v>
+        <v>1.7549</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3065</v>
+        <v>0.7570999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3448</v>
+        <v>0.3298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9617000000000001</v>
+        <v>0.4271</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2073</v>
+        <v>-1.9521</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9973</v>
+        <v>-0.6629</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.204499999999999</v>
+        <v>-1.2892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,70 +1252,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7439</v>
+        <v>-4.9349</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6853</v>
+        <v>-5.2585</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05859999999999999</v>
+        <v>0.3237000000000003</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.379</v>
+        <v>-10.9308</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2921</v>
+        <v>-4.2114</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0867</v>
+        <v>-6.7195</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4275</v>
+        <v>-5.847199999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5329999999999999</v>
+        <v>-0.8313</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9605</v>
+        <v>-5.016</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9515</v>
+        <v>-5.0836</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8253</v>
+        <v>-3.3802</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1262</v>
+        <v>-1.7034</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1699</v>
+        <v>7.214499999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9248</v>
+        <v>-1.3649</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7549</v>
+        <v>8.5794</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7570999999999999</v>
+        <v>-1.3375</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3298</v>
+        <v>-0.155</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4271</v>
+        <v>-1.1827</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9521</v>
+        <v>0.1192</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6629</v>
+        <v>2.1087</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2892</v>
+        <v>-1.9895</v>
       </c>
     </row>
     <row r="12">
@@ -1399,7 +1399,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SUAREZ CUSTODIO</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.549899999999999</v>
+        <v>-10.3582</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8736</v>
+        <v>-8.6198</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3237000000000003</v>
+        <v>-1.7384</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.5459</v>
+        <v>-7.4772</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.8265</v>
+        <v>-2.5827</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.7195</v>
+        <v>-4.8945</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.462299999999999</v>
+        <v>-5.1639</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4463</v>
+        <v>-0.6514</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.016</v>
+        <v>-4.512499999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.0836</v>
+        <v>-2.3132</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.3802</v>
+        <v>-1.9313</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7034</v>
+        <v>-0.3819</v>
       </c>
       <c r="P13" t="n">
-        <v>7.214499999999999</v>
+        <v>0.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3649</v>
+        <v>-3.8997</v>
       </c>
       <c r="R13" t="n">
-        <v>8.5794</v>
+        <v>4.2897</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3375</v>
+        <v>-0.3268</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.155</v>
+        <v>0.1652</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1827</v>
+        <v>-0.4921</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1192</v>
+        <v>-2.9443</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1087</v>
+        <v>0.2786</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9895</v>
+        <v>-3.2229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,222 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.8965</v>
+        <v>-2.7889</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1322</v>
+        <v>7.847300000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.7641</v>
+        <v>-10.636</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.263599999999999</v>
+        <v>-14.129</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.632099999999999</v>
+        <v>-14.6613</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6315</v>
+        <v>0.5324</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9052000000000001</v>
+        <v>22.1651</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.9463</v>
+        <v>9.147599999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0411</v>
+        <v>13.0175</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.3584</v>
+        <v>-36.2938</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6858</v>
+        <v>-23.8094</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6725</v>
+        <v>-12.4844</v>
       </c>
       <c r="P14" t="n">
-        <v>0.78</v>
+        <v>12.6742</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.0446</v>
+        <v>-48.7466</v>
       </c>
       <c r="R14" t="n">
-        <v>6.8245</v>
+        <v>61.42059999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3482</v>
+        <v>1.810499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4831</v>
+        <v>6.67</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1349</v>
+        <v>-4.86</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.7609</v>
+        <v>-3.1449</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3344</v>
+        <v>27.75849999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.0953</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A. SANCHO PEREZ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-10.3582</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-8.6198</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.7384</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-7.4772</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-2.5827</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4.8945</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-5.1639</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.6514</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-4.512499999999999</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-2.3132</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.9313</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.3819</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-3.8997</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.2897</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.3268</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.1652</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.4921</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-2.9443</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-3.2229</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-2.789199999999999</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7.847199999999999</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-10.636</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-14.1292</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-14.6615</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.5323000000000029</v>
-      </c>
-      <c r="J16" t="n">
-        <v>22.16480000000001</v>
-      </c>
-      <c r="K16" t="n">
-        <v>9.147499999999999</v>
-      </c>
-      <c r="L16" t="n">
-        <v>13.0174</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-36.2938</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-23.8094</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-12.4844</v>
-      </c>
-      <c r="P16" t="n">
-        <v>12.6742</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-48.7466</v>
-      </c>
-      <c r="R16" t="n">
-        <v>61.42059999999999</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.8105</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-4.859999999999999</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-3.144899999999999</v>
-      </c>
-      <c r="W16" t="n">
-        <v>27.75849999999999</v>
-      </c>
-      <c r="X16" t="n">
         <v>-30.9031</v>
       </c>
     </row>
